--- a/data/raw/all_customers.xlsx
+++ b/data/raw/all_customers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,6 +696,106 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>오부장</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>경찰학원</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>010-2653-4166</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>부평구</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>45-80</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0-10000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0-400</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>{"region":"부평구","floor":"0-10","area_real":"45-80","deposit":"0-10000","rent":"0-400","premium":"0"}</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>darkbirth@naver.com</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-09-09T03:33:47.903Z</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>경찰청교육관_01026534166</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>생</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>45-80</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0-10000</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0-400</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
